--- a/tests/fixtures/ctpe_shape/batch2/no_the_finding/b2_no.xlsx
+++ b/tests/fixtures/ctpe_shape/batch2/no_the_finding/b2_no.xlsx
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44688.46527777778</v>
+        <v>47882.17013888889</v>
       </c>
       <c r="H2" t="n">
         <v>27.4</v>
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44688.46527777778</v>
+        <v>47882.17013888889</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
